--- a/samples/Prepaid_Committee_2022-2025.xlsx
+++ b/samples/Prepaid_Committee_2022-2025.xlsx
@@ -878,8 +878,16 @@
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>9.78%</t>
+        </is>
+      </c>
       <c r="J6" s="10" t="n">
         <v>1</v>
       </c>
@@ -1051,7 +1059,7 @@
       <c r="N8" s="9" t="inlineStr"/>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>$5.5M</t>
+          <t>$5.54M</t>
         </is>
       </c>
       <c r="P8" s="9" t="inlineStr"/>
@@ -1272,7 +1280,7 @@
       </c>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>$1.2M</t>
+          <t>$1.17M</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr"/>
@@ -1412,7 +1420,7 @@
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>$2.1B</t>
+          <t>$2.14B</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
@@ -1422,12 +1430,12 @@
       </c>
       <c r="O13" s="9" t="inlineStr">
         <is>
-          <t>$229.8M</t>
+          <t>$229.77M</t>
         </is>
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>$3.2B</t>
+          <t>$3.16B</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr"/>
@@ -1647,7 +1655,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>$1.6B</t>
+          <t>$1.62B</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
@@ -1708,7 +1716,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>11.67%</t>
+        </is>
+      </c>
       <c r="J17" s="10" t="n">
         <v>1</v>
       </c>
@@ -2632,7 +2644,11 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J8" s="10" t="n">
         <v>1</v>
       </c>
@@ -2653,7 +2669,7 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -2721,7 +2737,7 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>$1.1B</t>
+          <t>$1.15B</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
@@ -2891,7 +2907,7 @@
       </c>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>$1.2M</t>
+          <t>$1.17M</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr"/>
@@ -3035,7 +3051,7 @@
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>$2.2B</t>
+          <t>$2.23B</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
@@ -3050,7 +3066,7 @@
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>$3.4B</t>
+          <t>$3.39B</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr"/>
@@ -3112,7 +3128,7 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>$1.2B</t>
+          <t>$1.17B</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
@@ -3122,12 +3138,12 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>$44.1M</t>
+          <t>$44.11M</t>
         </is>
       </c>
       <c r="P14" s="9" t="inlineStr">
         <is>
-          <t>$255.2M</t>
+          <t>$255.16M</t>
         </is>
       </c>
       <c r="Q14" s="9" t="inlineStr">
@@ -3208,7 +3224,7 @@
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>$2.7B</t>
+          <t>$2.68B</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr"/>
@@ -3270,7 +3286,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>$1.6B</t>
+          <t>$1.61B</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
@@ -3471,7 +3487,7 @@
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>$1.3B</t>
+          <t>$1.29B</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr"/>
@@ -3845,7 +3861,7 @@
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>$338.6M</t>
+          <t>$338.63M</t>
         </is>
       </c>
       <c r="N24" s="9" t="inlineStr">
@@ -3855,12 +3871,12 @@
       </c>
       <c r="O24" s="9" t="inlineStr">
         <is>
-          <t>$90.5M</t>
+          <t>$90.45M</t>
         </is>
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>$2.5B</t>
+          <t>$2.51B</t>
         </is>
       </c>
       <c r="Q24" s="9" t="inlineStr">
@@ -4210,7 +4226,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,370,000</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
@@ -4220,7 +4236,7 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>$7.1B</t>
+          <t>$7.11B</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr"/>
@@ -4291,7 +4307,7 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -4334,8 +4350,16 @@
       </c>
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>3% for next 3 years, then 5% for next 5 years</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr"/>
       <c r="K9" s="9" t="n">
         <v/>
@@ -4414,7 +4438,7 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>MET I: $103.5M  MET II: $1.1B</t>
+          <t>MET I: $103.5M  MET II: $1.06B</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
@@ -4740,7 +4764,7 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>$1.3B</t>
+          <t>$1.27B</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
@@ -4840,7 +4864,7 @@
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>$2.9B</t>
+          <t>$2.86B</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr"/>
@@ -4906,7 +4930,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>$1.8B</t>
+          <t>$1.75B</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
@@ -4921,7 +4945,7 @@
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>$3.0B</t>
+          <t>$3B</t>
         </is>
       </c>
       <c r="Q16" s="9" t="inlineStr">
@@ -5114,7 +5138,7 @@
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>$1.4B</t>
+          <t>$1.37B</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr"/>
@@ -5881,7 +5905,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,370,000</t>
         </is>
       </c>
       <c r="O7" s="9" t="inlineStr">
@@ -5891,7 +5915,7 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>$7.2B</t>
+          <t>$7.19B</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr"/>
@@ -5962,7 +5986,7 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -5993,12 +6017,28 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Yes (legislative)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Yes (in state only)</t>
+        </is>
+      </c>
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>3% for next 3 years, then 5% for next 5 years</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr"/>
       <c r="K9" s="9" t="n">
         <v/>
@@ -6077,7 +6117,7 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>MET I: $105.7M  MET II: $1.1B</t>
+          <t>MET I: $105.7M  MET II: $1.08B</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
@@ -6091,7 +6131,11 @@
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr"/>
-      <c r="Q10" s="9" t="inlineStr"/>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>All data is as of 9/30/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -6139,8 +6183,10 @@
           <t>Horizon: 5.5% Legacy: 5.5%</t>
         </is>
       </c>
-      <c r="J11" s="10" t="n">
-        <v>1.4</v>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Horizon: 140.0%  Legacy: 106%</t>
+        </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
@@ -6331,7 +6377,7 @@
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>$3.8B</t>
+          <t>$3.82B</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
@@ -6401,7 +6447,7 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>$1.3B</t>
+          <t>$1.33B</t>
         </is>
       </c>
       <c r="N14" s="9" t="inlineStr">
@@ -6501,7 +6547,7 @@
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>$3.0B</t>
+          <t>$3.03B</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr"/>
@@ -6567,7 +6613,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>$1.9B</t>
+          <t>$1.89B</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
@@ -6775,7 +6821,7 @@
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>$1.3B</t>
+          <t>$1.348B</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr"/>
@@ -6856,7 +6902,7 @@
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>$1.8B</t>
+          <t>$1.75B</t>
         </is>
       </c>
       <c r="Q20" s="9" t="inlineStr">
@@ -7196,7 +7242,7 @@
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>$2.6B</t>
+          <t>$2.62B</t>
         </is>
       </c>
       <c r="Q24" s="9" t="inlineStr">
